--- a/MixingStationChannelList.xlsx
+++ b/MixingStationChannelList.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3495" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3507" uniqueCount="539">
   <si>
     <t xml:space="preserve">Enabled</t>
   </si>
@@ -280,9 +280,6 @@
   </si>
   <si>
     <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
   </si>
   <si>
     <t xml:space="preserve">x</t>
@@ -2831,10 +2828,10 @@
         <v>77</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>10</v>
+        <v>77</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>77</v>
@@ -2927,7 +2924,7 @@
         <v>73</v>
       </c>
       <c r="AS2" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT2" s="10"/>
       <c r="AU2" s="10"/>
@@ -2953,7 +2950,7 @@
       <c r="BO2" s="10"/>
       <c r="BP2" s="10"/>
       <c r="BR2" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS2" s="10"/>
       <c r="BT2" s="10"/>
@@ -3164,7 +3161,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>75</v>
@@ -3185,10 +3182,10 @@
         <v>77</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>-99</v>
+        <v>77</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>77</v>
@@ -3281,7 +3278,7 @@
         <v>73</v>
       </c>
       <c r="AS3" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT3" s="10"/>
       <c r="AU3" s="10"/>
@@ -3307,7 +3304,7 @@
       <c r="BO3" s="10"/>
       <c r="BP3" s="10"/>
       <c r="BR3" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS3" s="10"/>
       <c r="BT3" s="10"/>
@@ -3518,7 +3515,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>75</v>
@@ -3539,10 +3536,10 @@
         <v>77</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>10</v>
+        <v>77</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>77</v>
@@ -3635,7 +3632,7 @@
         <v>73</v>
       </c>
       <c r="AS4" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT4" s="10"/>
       <c r="AU4" s="10"/>
@@ -3661,7 +3658,7 @@
       <c r="BO4" s="10"/>
       <c r="BP4" s="10"/>
       <c r="BR4" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS4" s="10"/>
       <c r="BT4" s="10"/>
@@ -3872,7 +3869,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>75</v>
@@ -3893,10 +3890,10 @@
         <v>77</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>-99</v>
+        <v>77</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L5" s="10" t="s">
         <v>77</v>
@@ -3989,7 +3986,7 @@
         <v>73</v>
       </c>
       <c r="AS5" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT5" s="10"/>
       <c r="AU5" s="10"/>
@@ -4015,7 +4012,7 @@
       <c r="BO5" s="10"/>
       <c r="BP5" s="10"/>
       <c r="BR5" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS5" s="10"/>
       <c r="BT5" s="10"/>
@@ -4226,7 +4223,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>75</v>
@@ -4247,10 +4244,10 @@
         <v>77</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>10</v>
+        <v>77</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>77</v>
@@ -4343,7 +4340,7 @@
         <v>73</v>
       </c>
       <c r="AS6" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT6" s="10"/>
       <c r="AU6" s="10"/>
@@ -4369,7 +4366,7 @@
       <c r="BO6" s="10"/>
       <c r="BP6" s="10"/>
       <c r="BR6" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS6" s="10"/>
       <c r="BT6" s="10"/>
@@ -4580,7 +4577,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>75</v>
@@ -4601,10 +4598,10 @@
         <v>77</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>-99</v>
+        <v>77</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>77</v>
@@ -4697,7 +4694,7 @@
         <v>73</v>
       </c>
       <c r="AS7" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT7" s="10"/>
       <c r="AU7" s="10"/>
@@ -4723,7 +4720,7 @@
       <c r="BO7" s="10"/>
       <c r="BP7" s="10"/>
       <c r="BR7" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS7" s="10"/>
       <c r="BT7" s="10"/>
@@ -4934,7 +4931,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>75</v>
@@ -4955,10 +4952,10 @@
         <v>77</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>10</v>
+        <v>77</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>77</v>
@@ -5051,7 +5048,7 @@
         <v>73</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT8" s="10"/>
       <c r="AU8" s="10"/>
@@ -5077,7 +5074,7 @@
       <c r="BO8" s="10"/>
       <c r="BP8" s="10"/>
       <c r="BR8" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS8" s="10"/>
       <c r="BT8" s="10"/>
@@ -5288,7 +5285,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>75</v>
@@ -5309,10 +5306,10 @@
         <v>77</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>-99</v>
+        <v>77</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>77</v>
@@ -5405,7 +5402,7 @@
         <v>73</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT9" s="10"/>
       <c r="AU9" s="10"/>
@@ -5431,7 +5428,7 @@
       <c r="BO9" s="10"/>
       <c r="BP9" s="10"/>
       <c r="BR9" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS9" s="10"/>
       <c r="BT9" s="10"/>
@@ -5642,7 +5639,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>75</v>
@@ -5663,10 +5660,10 @@
         <v>77</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>10</v>
+        <v>77</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>77</v>
@@ -5759,7 +5756,7 @@
         <v>73</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT10" s="10"/>
       <c r="AU10" s="10"/>
@@ -5785,7 +5782,7 @@
       <c r="BO10" s="10"/>
       <c r="BP10" s="10"/>
       <c r="BR10" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS10" s="10"/>
       <c r="BT10" s="10"/>
@@ -5996,7 +5993,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>75</v>
@@ -6017,10 +6014,10 @@
         <v>77</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>-99</v>
+        <v>77</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>77</v>
@@ -6113,7 +6110,7 @@
         <v>73</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT11" s="10"/>
       <c r="AU11" s="10"/>
@@ -6139,7 +6136,7 @@
       <c r="BO11" s="10"/>
       <c r="BP11" s="10"/>
       <c r="BR11" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS11" s="10"/>
       <c r="BT11" s="10"/>
@@ -6350,7 +6347,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>75</v>
@@ -6371,10 +6368,10 @@
         <v>77</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>10</v>
+        <v>77</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>77</v>
@@ -6467,7 +6464,7 @@
         <v>73</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT12" s="10"/>
       <c r="AU12" s="10"/>
@@ -6493,7 +6490,7 @@
       <c r="BO12" s="10"/>
       <c r="BP12" s="10"/>
       <c r="BR12" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS12" s="10"/>
       <c r="BT12" s="10"/>
@@ -6704,7 +6701,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>75</v>
@@ -6725,10 +6722,10 @@
         <v>77</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>-99</v>
+        <v>77</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>77</v>
@@ -6821,7 +6818,7 @@
         <v>73</v>
       </c>
       <c r="AS13" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AT13" s="10"/>
       <c r="AU13" s="10"/>
@@ -6847,7 +6844,7 @@
       <c r="BO13" s="10"/>
       <c r="BP13" s="10"/>
       <c r="BR13" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS13" s="10"/>
       <c r="BT13" s="10"/>
@@ -7058,7 +7055,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>75</v>
@@ -7176,7 +7173,7 @@
       </c>
       <c r="AS14" s="10"/>
       <c r="AT14" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AU14" s="10"/>
       <c r="AV14" s="10"/>
@@ -7201,7 +7198,7 @@
       <c r="BO14" s="10"/>
       <c r="BP14" s="10"/>
       <c r="BR14" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS14" s="10"/>
       <c r="BT14" s="10"/>
@@ -7412,10 +7409,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>76</v>
@@ -7553,7 +7550,7 @@
       <c r="BO15" s="10"/>
       <c r="BP15" s="10"/>
       <c r="BR15" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS15" s="10"/>
       <c r="BT15" s="10"/>
@@ -7764,10 +7761,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>76</v>
@@ -7905,7 +7902,7 @@
       <c r="BO16" s="10"/>
       <c r="BP16" s="10"/>
       <c r="BR16" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS16" s="10"/>
       <c r="BT16" s="10"/>
@@ -8116,10 +8113,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -8257,7 +8254,7 @@
       <c r="BO17" s="10"/>
       <c r="BP17" s="10"/>
       <c r="BR17" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS17" s="10"/>
       <c r="BT17" s="10"/>
@@ -8468,10 +8465,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>76</v>
@@ -8587,7 +8584,7 @@
       <c r="AS18" s="10"/>
       <c r="AT18" s="10"/>
       <c r="AU18" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AV18" s="10"/>
       <c r="AW18" s="10"/>
@@ -8611,7 +8608,7 @@
       <c r="BO18" s="10"/>
       <c r="BP18" s="10"/>
       <c r="BR18" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS18" s="10"/>
       <c r="BT18" s="10"/>
@@ -8822,10 +8819,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>76</v>
@@ -8941,7 +8938,7 @@
       <c r="AS19" s="10"/>
       <c r="AT19" s="10"/>
       <c r="AU19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AV19" s="10"/>
       <c r="AW19" s="10"/>
@@ -8965,7 +8962,7 @@
       <c r="BO19" s="10"/>
       <c r="BP19" s="10"/>
       <c r="BR19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS19" s="10"/>
       <c r="BT19" s="10"/>
@@ -9176,10 +9173,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>76</v>
@@ -9296,7 +9293,7 @@
       <c r="AT20" s="10"/>
       <c r="AU20" s="10"/>
       <c r="AV20" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW20" s="10"/>
       <c r="AX20" s="10"/>
@@ -9319,7 +9316,7 @@
       <c r="BO20" s="10"/>
       <c r="BP20" s="10"/>
       <c r="BR20" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS20" s="10"/>
       <c r="BT20" s="10"/>
@@ -9530,10 +9527,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>76</v>
@@ -9650,7 +9647,7 @@
       <c r="AT21" s="10"/>
       <c r="AU21" s="10"/>
       <c r="AV21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW21" s="10"/>
       <c r="AX21" s="10"/>
@@ -9673,7 +9670,7 @@
       <c r="BO21" s="10"/>
       <c r="BP21" s="10"/>
       <c r="BR21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS21" s="10"/>
       <c r="BT21" s="10"/>
@@ -9884,10 +9881,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>76</v>
@@ -10004,7 +10001,7 @@
       <c r="AT22" s="10"/>
       <c r="AU22" s="10"/>
       <c r="AV22" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW22" s="10"/>
       <c r="AX22" s="10"/>
@@ -10027,7 +10024,7 @@
       <c r="BO22" s="10"/>
       <c r="BP22" s="10"/>
       <c r="BR22" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS22" s="10"/>
       <c r="BT22" s="10"/>
@@ -10238,10 +10235,10 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>76</v>
@@ -10358,7 +10355,7 @@
       <c r="AT23" s="10"/>
       <c r="AU23" s="10"/>
       <c r="AV23" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW23" s="10"/>
       <c r="AX23" s="10"/>
@@ -10381,7 +10378,7 @@
       <c r="BO23" s="10"/>
       <c r="BP23" s="10"/>
       <c r="BR23" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS23" s="10"/>
       <c r="BT23" s="10"/>
@@ -10592,10 +10589,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>76</v>
@@ -10712,7 +10709,7 @@
       <c r="AT24" s="10"/>
       <c r="AU24" s="10"/>
       <c r="AV24" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW24" s="10"/>
       <c r="AX24" s="10"/>
@@ -10735,7 +10732,7 @@
       <c r="BO24" s="10"/>
       <c r="BP24" s="10"/>
       <c r="BR24" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS24" s="10"/>
       <c r="BT24" s="10"/>
@@ -10946,10 +10943,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>76</v>
@@ -11066,7 +11063,7 @@
       <c r="AT25" s="10"/>
       <c r="AU25" s="10"/>
       <c r="AV25" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AW25" s="10"/>
       <c r="AX25" s="10"/>
@@ -11089,7 +11086,7 @@
       <c r="BO25" s="10"/>
       <c r="BP25" s="10"/>
       <c r="BR25" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS25" s="10"/>
       <c r="BT25" s="10"/>
@@ -11300,10 +11297,10 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>105</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>76</v>
@@ -11421,7 +11418,7 @@
       <c r="AU26" s="10"/>
       <c r="AV26" s="10"/>
       <c r="AW26" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AX26" s="10"/>
       <c r="AY26" s="10"/>
@@ -11443,7 +11440,7 @@
       <c r="BO26" s="10"/>
       <c r="BP26" s="10"/>
       <c r="BR26" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS26" s="10"/>
       <c r="BT26" s="10"/>
@@ -11654,10 +11651,10 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>76</v>
@@ -11775,7 +11772,7 @@
       <c r="AU27" s="10"/>
       <c r="AV27" s="10"/>
       <c r="AW27" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AX27" s="10"/>
       <c r="AY27" s="10"/>
@@ -11797,7 +11794,7 @@
       <c r="BO27" s="10"/>
       <c r="BP27" s="10"/>
       <c r="BR27" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS27" s="10"/>
       <c r="BT27" s="10"/>
@@ -12008,10 +12005,10 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>76</v>
@@ -12123,7 +12120,7 @@
       <c r="AU28" s="10"/>
       <c r="AV28" s="10"/>
       <c r="AW28" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AX28" s="10"/>
       <c r="AY28" s="10"/>
@@ -12145,7 +12142,7 @@
       <c r="BO28" s="10"/>
       <c r="BP28" s="10"/>
       <c r="BR28" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS28" s="10"/>
       <c r="BT28" s="10"/>
@@ -12356,10 +12353,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>76</v>
@@ -12477,7 +12474,7 @@
       <c r="AU29" s="10"/>
       <c r="AV29" s="10"/>
       <c r="AW29" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AX29" s="10"/>
       <c r="AY29" s="10"/>
@@ -12499,7 +12496,7 @@
       <c r="BO29" s="10"/>
       <c r="BP29" s="10"/>
       <c r="BR29" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS29" s="10"/>
       <c r="BT29" s="10"/>
@@ -12710,10 +12707,10 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>76</v>
@@ -12832,7 +12829,7 @@
       <c r="AV30" s="10"/>
       <c r="AW30" s="10"/>
       <c r="AX30" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY30" s="10"/>
       <c r="AZ30" s="10"/>
@@ -12853,7 +12850,7 @@
       <c r="BO30" s="10"/>
       <c r="BP30" s="10"/>
       <c r="BR30" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS30" s="10"/>
       <c r="BT30" s="10"/>
@@ -13064,10 +13061,10 @@
         <v>30</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>76</v>
@@ -13186,7 +13183,7 @@
       <c r="AV31" s="10"/>
       <c r="AW31" s="10"/>
       <c r="AX31" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY31" s="10"/>
       <c r="AZ31" s="10"/>
@@ -13207,7 +13204,7 @@
       <c r="BO31" s="10"/>
       <c r="BP31" s="10"/>
       <c r="BR31" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS31" s="10"/>
       <c r="BT31" s="10"/>
@@ -13418,10 +13415,10 @@
         <v>31</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>76</v>
@@ -13540,7 +13537,7 @@
       <c r="AV32" s="10"/>
       <c r="AW32" s="10"/>
       <c r="AX32" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY32" s="10"/>
       <c r="AZ32" s="10"/>
@@ -13561,7 +13558,7 @@
       <c r="BO32" s="10"/>
       <c r="BP32" s="10"/>
       <c r="BR32" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS32" s="10"/>
       <c r="BT32" s="10"/>
@@ -13772,10 +13769,10 @@
         <v>32</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>76</v>
@@ -13894,7 +13891,7 @@
       <c r="AV33" s="10"/>
       <c r="AW33" s="10"/>
       <c r="AX33" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY33" s="10"/>
       <c r="AZ33" s="10"/>
@@ -13915,7 +13912,7 @@
       <c r="BO33" s="10"/>
       <c r="BP33" s="10"/>
       <c r="BR33" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS33" s="10"/>
       <c r="BT33" s="10"/>
@@ -14126,10 +14123,10 @@
         <v>33</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>76</v>
@@ -14248,7 +14245,7 @@
       <c r="AV34" s="10"/>
       <c r="AW34" s="10"/>
       <c r="AX34" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY34" s="10"/>
       <c r="AZ34" s="10"/>
@@ -14269,7 +14266,7 @@
       <c r="BO34" s="10"/>
       <c r="BP34" s="10"/>
       <c r="BR34" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS34" s="10"/>
       <c r="BT34" s="10"/>
@@ -14480,10 +14477,10 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>76</v>
@@ -14602,7 +14599,7 @@
       <c r="AV35" s="10"/>
       <c r="AW35" s="10"/>
       <c r="AX35" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY35" s="10"/>
       <c r="AZ35" s="10"/>
@@ -14623,7 +14620,7 @@
       <c r="BO35" s="10"/>
       <c r="BP35" s="10"/>
       <c r="BR35" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS35" s="10"/>
       <c r="BT35" s="10"/>
@@ -14834,10 +14831,10 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>76</v>
@@ -14956,7 +14953,7 @@
       <c r="AV36" s="10"/>
       <c r="AW36" s="10"/>
       <c r="AX36" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY36" s="10"/>
       <c r="AZ36" s="10"/>
@@ -14977,7 +14974,7 @@
       <c r="BO36" s="10"/>
       <c r="BP36" s="10"/>
       <c r="BR36" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS36" s="10"/>
       <c r="BT36" s="10"/>
@@ -15188,10 +15185,10 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>76</v>
@@ -15310,7 +15307,7 @@
       <c r="AV37" s="10"/>
       <c r="AW37" s="10"/>
       <c r="AX37" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AY37" s="10"/>
       <c r="AZ37" s="10"/>
@@ -15331,7 +15328,7 @@
       <c r="BO37" s="10"/>
       <c r="BP37" s="10"/>
       <c r="BR37" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS37" s="10"/>
       <c r="BT37" s="10"/>
@@ -15542,10 +15539,10 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>76</v>
@@ -15683,7 +15680,7 @@
       <c r="BO38" s="10"/>
       <c r="BP38" s="10"/>
       <c r="BR38" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS38" s="10"/>
       <c r="BT38" s="10"/>
@@ -15894,10 +15891,10 @@
         <v>38</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>76</v>
@@ -16035,7 +16032,7 @@
       <c r="BO39" s="10"/>
       <c r="BP39" s="10"/>
       <c r="BR39" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS39" s="10"/>
       <c r="BT39" s="10"/>
@@ -16246,10 +16243,10 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>76</v>
@@ -16387,7 +16384,7 @@
       <c r="BO40" s="10"/>
       <c r="BP40" s="10"/>
       <c r="BR40" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS40" s="10"/>
       <c r="BT40" s="10"/>
@@ -16598,10 +16595,10 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>76</v>
@@ -16739,7 +16736,7 @@
       <c r="BO41" s="10"/>
       <c r="BP41" s="10"/>
       <c r="BR41" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BS41" s="10"/>
       <c r="BT41" s="10"/>
@@ -16950,10 +16947,10 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>76</v>
@@ -17073,7 +17070,7 @@
       <c r="AW42" s="10"/>
       <c r="AX42" s="10"/>
       <c r="AY42" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AZ42" s="10"/>
       <c r="BA42" s="10"/>
@@ -17094,7 +17091,7 @@
       <c r="BP42" s="10"/>
       <c r="BR42" s="10"/>
       <c r="BS42" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT42" s="10"/>
       <c r="BU42" s="10"/>
@@ -17304,10 +17301,10 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>76</v>
@@ -17427,7 +17424,7 @@
       <c r="AW43" s="10"/>
       <c r="AX43" s="10"/>
       <c r="AY43" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AZ43" s="10"/>
       <c r="BA43" s="10"/>
@@ -17448,7 +17445,7 @@
       <c r="BP43" s="10"/>
       <c r="BR43" s="10"/>
       <c r="BS43" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT43" s="10"/>
       <c r="BU43" s="10"/>
@@ -17658,10 +17655,10 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>76</v>
@@ -17781,7 +17778,7 @@
       <c r="AW44" s="10"/>
       <c r="AX44" s="10"/>
       <c r="AY44" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AZ44" s="10"/>
       <c r="BA44" s="10"/>
@@ -17802,7 +17799,7 @@
       <c r="BP44" s="10"/>
       <c r="BR44" s="10"/>
       <c r="BS44" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT44" s="10"/>
       <c r="BU44" s="10"/>
@@ -18012,10 +18009,10 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>76</v>
@@ -18135,7 +18132,7 @@
       <c r="AW45" s="10"/>
       <c r="AX45" s="10"/>
       <c r="AY45" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AZ45" s="10"/>
       <c r="BA45" s="10"/>
@@ -18156,7 +18153,7 @@
       <c r="BP45" s="10"/>
       <c r="BR45" s="10"/>
       <c r="BS45" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT45" s="10"/>
       <c r="BU45" s="10"/>
@@ -18366,10 +18363,10 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>76</v>
@@ -18490,7 +18487,7 @@
       <c r="AX46" s="10"/>
       <c r="AY46" s="10"/>
       <c r="AZ46" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BA46" s="10"/>
       <c r="BB46" s="10"/>
@@ -18510,7 +18507,7 @@
       <c r="BP46" s="10"/>
       <c r="BR46" s="10"/>
       <c r="BS46" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT46" s="10"/>
       <c r="BU46" s="10"/>
@@ -18720,10 +18717,10 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>76</v>
@@ -18844,7 +18841,7 @@
       <c r="AX47" s="10"/>
       <c r="AY47" s="10"/>
       <c r="AZ47" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BA47" s="10"/>
       <c r="BB47" s="10"/>
@@ -18864,7 +18861,7 @@
       <c r="BP47" s="10"/>
       <c r="BR47" s="10"/>
       <c r="BS47" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT47" s="10"/>
       <c r="BU47" s="10"/>
@@ -19074,10 +19071,10 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>76</v>
@@ -19198,7 +19195,7 @@
       <c r="AX48" s="10"/>
       <c r="AY48" s="10"/>
       <c r="AZ48" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BA48" s="10"/>
       <c r="BB48" s="10"/>
@@ -19218,7 +19215,7 @@
       <c r="BP48" s="10"/>
       <c r="BR48" s="10"/>
       <c r="BS48" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT48" s="10"/>
       <c r="BU48" s="10"/>
@@ -19428,10 +19425,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>76</v>
@@ -19552,7 +19549,7 @@
       <c r="AX49" s="10"/>
       <c r="AY49" s="10"/>
       <c r="AZ49" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BA49" s="10"/>
       <c r="BB49" s="10"/>
@@ -19572,7 +19569,7 @@
       <c r="BP49" s="10"/>
       <c r="BR49" s="10"/>
       <c r="BS49" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BT49" s="10"/>
       <c r="BU49" s="10"/>
@@ -20615,49 +20612,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="F1" s="17"/>
       <c r="G1" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>134</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>135</v>
       </c>
       <c r="J1" s="17"/>
       <c r="K1" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="L1" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="19" t="s">
         <v>137</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>138</v>
       </c>
       <c r="N1" s="17"/>
       <c r="O1" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="P1" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>140</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21113,7 +21110,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -21936,7 +21933,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>32</v>
@@ -22325,7 +22322,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>48</v>
@@ -22696,7 +22693,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>64</v>
@@ -22722,7 +22719,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>65</v>
@@ -23145,7 +23142,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>95</v>
@@ -23162,7 +23159,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>96</v>
@@ -23613,7 +23610,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>128</v>
@@ -23697,125 +23694,125 @@
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>152</v>
       </c>
       <c r="D1" s="23"/>
       <c r="E1" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="G1" s="24" t="s">
         <v>154</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>155</v>
       </c>
       <c r="H1" s="23"/>
       <c r="I1" s="23"/>
       <c r="J1" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="L1" s="24" t="s">
         <v>157</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>158</v>
       </c>
       <c r="M1" s="23"/>
       <c r="N1" s="23"/>
       <c r="O1" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="P1" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="Q1" s="25" t="s">
         <v>160</v>
-      </c>
-      <c r="Q1" s="25" t="s">
-        <v>161</v>
       </c>
       <c r="R1" s="23"/>
       <c r="S1" s="23"/>
       <c r="T1" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="U1" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="U1" s="25" t="s">
+      <c r="V1" s="25" t="s">
         <v>163</v>
-      </c>
-      <c r="V1" s="25" t="s">
-        <v>164</v>
       </c>
       <c r="W1" s="23"/>
       <c r="X1" s="23"/>
       <c r="Y1" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z1" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="Z1" s="26" t="s">
+      <c r="AA1" s="26" t="s">
         <v>166</v>
-      </c>
-      <c r="AA1" s="26" t="s">
-        <v>167</v>
       </c>
       <c r="AB1" s="23"/>
       <c r="AC1" s="23"/>
       <c r="AD1" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE1" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="AE1" s="26" t="s">
+      <c r="AF1" s="26" t="s">
         <v>169</v>
-      </c>
-      <c r="AF1" s="26" t="s">
-        <v>170</v>
       </c>
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ1" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="AJ1" s="24" t="s">
+      <c r="AK1" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="AK1" s="24" t="s">
+      <c r="AN1" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="AN1" s="24" t="s">
+      <c r="AO1" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="AO1" s="24" t="s">
+      <c r="AP1" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="AP1" s="24" t="s">
+      <c r="AS1" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="AS1" s="27" t="s">
+      <c r="AT1" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="AT1" s="27" t="s">
+      <c r="AU1" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="AU1" s="27" t="s">
+      <c r="AW1" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="AW1" s="24" t="s">
+      <c r="AX1" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="AX1" s="24" t="s">
+      <c r="AY1" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="AY1" s="24" t="s">
+      <c r="BA1" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="BA1" s="27" t="s">
+      <c r="BB1" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="BB1" s="27" t="s">
+      <c r="BC1" s="27" t="s">
         <v>184</v>
-      </c>
-      <c r="BC1" s="27" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23823,7 +23820,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C2" s="30" t="s">
         <v>75</v>
@@ -23832,10 +23829,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H2" s="2" t="n">
         <f aca="false">IF(F2&lt;&gt;CONCATENATE("Aux",E2),1,0)</f>
@@ -23845,10 +23842,10 @@
         <v>1</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L2" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M2" s="2" t="n">
         <f aca="false">IF(K2&lt;&gt;CONCATENATE("STAux",J2),1,0)</f>
@@ -23886,10 +23883,10 @@
         <v>1</v>
       </c>
       <c r="Z2" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AA2" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB2" s="2" t="n">
         <f aca="false">IF(Z2&lt;&gt;CONCATENATE("Mtx",Y2),1,0)</f>
@@ -23900,10 +23897,10 @@
         <v>1</v>
       </c>
       <c r="AE2" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AF2" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG2" s="2" t="n">
         <f aca="false">IF(AE2&lt;&gt;CONCATENATE("StMtx",AD2),1,0)</f>
@@ -23913,10 +23910,10 @@
         <v>1</v>
       </c>
       <c r="AJ2" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AK2" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL2" s="2" t="n">
         <f aca="false">IF(AJ2&lt;&gt;CONCATENATE("Fx",AI2),1,0)</f>
@@ -23927,10 +23924,10 @@
         <v>1</v>
       </c>
       <c r="AO2" s="31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AP2" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="2" t="n">
         <f aca="false">IF(AO2&lt;&gt;CONCATENATE("StFx",AN2),1,0)</f>
@@ -23941,29 +23938,29 @@
         <v>1</v>
       </c>
       <c r="AT2" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AU2" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW2" s="28" t="n">
         <v>1</v>
       </c>
       <c r="AX2" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AY2" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ2" s="2"/>
       <c r="BA2" s="28" t="n">
         <v>1</v>
       </c>
       <c r="BB2" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BC2" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23971,7 +23968,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C3" s="30" t="s">
         <v>75</v>
@@ -23980,10 +23977,10 @@
         <v>2</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H3" s="2" t="n">
         <f aca="false">IF(F3&lt;&gt;CONCATENATE("Aux",E3),1,0)</f>
@@ -23993,10 +23990,10 @@
         <v>2</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M3" s="2" t="n">
         <f aca="false">IF(K3&lt;&gt;CONCATENATE("STAux",J3),1,0)</f>
@@ -24034,10 +24031,10 @@
         <v>2</v>
       </c>
       <c r="Z3" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AA3" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB3" s="2" t="n">
         <f aca="false">IF(Z3&lt;&gt;CONCATENATE("Mtx",Y3),1,0)</f>
@@ -24048,10 +24045,10 @@
         <v>2</v>
       </c>
       <c r="AE3" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AF3" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG3" s="2" t="n">
         <f aca="false">IF(AE3&lt;&gt;CONCATENATE("StMtx",AD3),1,0)</f>
@@ -24061,10 +24058,10 @@
         <v>2</v>
       </c>
       <c r="AJ3" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AK3" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL3" s="2" t="n">
         <f aca="false">IF(AJ3&lt;&gt;CONCATENATE("Fx",AI3),1,0)</f>
@@ -24075,10 +24072,10 @@
         <v>2</v>
       </c>
       <c r="AO3" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AP3" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ3" s="2" t="n">
         <f aca="false">IF(AO3&lt;&gt;CONCATENATE("StFx",AN3),1,0)</f>
@@ -24089,29 +24086,29 @@
         <v>2</v>
       </c>
       <c r="AT3" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AU3" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW3" s="28" t="n">
         <v>2</v>
       </c>
       <c r="AX3" s="31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AY3" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ3" s="2"/>
       <c r="BA3" s="28" t="n">
         <v>2</v>
       </c>
       <c r="BB3" s="31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC3" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24119,19 +24116,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E4" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H4" s="2" t="n">
         <f aca="false">IF(F4&lt;&gt;CONCATENATE("Aux",E4),1,0)</f>
@@ -24141,10 +24138,10 @@
         <v>3</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M4" s="2" t="n">
         <f aca="false">IF(K4&lt;&gt;CONCATENATE("STAux",J4),1,0)</f>
@@ -24182,10 +24179,10 @@
         <v>3</v>
       </c>
       <c r="Z4" s="31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AA4" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB4" s="2" t="n">
         <f aca="false">IF(Z4&lt;&gt;CONCATENATE("Mtx",Y4),1,0)</f>
@@ -24196,10 +24193,10 @@
         <v>3</v>
       </c>
       <c r="AE4" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF4" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG4" s="2" t="n">
         <f aca="false">IF(AE4&lt;&gt;CONCATENATE("StMtx",AD4),1,0)</f>
@@ -24209,10 +24206,10 @@
         <v>3</v>
       </c>
       <c r="AJ4" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL4" s="2" t="n">
         <f aca="false">IF(AJ4&lt;&gt;CONCATENATE("Fx",AI4),1,0)</f>
@@ -24223,10 +24220,10 @@
         <v>3</v>
       </c>
       <c r="AO4" s="31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AP4" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ4" s="2" t="n">
         <f aca="false">IF(AO4&lt;&gt;CONCATENATE("StFx",AN4),1,0)</f>
@@ -24237,29 +24234,29 @@
         <v>3</v>
       </c>
       <c r="AT4" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AU4" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW4" s="28" t="n">
         <v>3</v>
       </c>
       <c r="AX4" s="31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AY4" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ4" s="2"/>
       <c r="BA4" s="28" t="n">
         <v>3</v>
       </c>
       <c r="BB4" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BC4" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24267,19 +24264,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H5" s="2" t="n">
         <f aca="false">IF(F5&lt;&gt;CONCATENATE("Aux",E5),1,0)</f>
@@ -24289,10 +24286,10 @@
         <v>4</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M5" s="2" t="n">
         <f aca="false">IF(K5&lt;&gt;CONCATENATE("STAux",J5),1,0)</f>
@@ -24330,10 +24327,10 @@
         <v>4</v>
       </c>
       <c r="Z5" s="31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB5" s="2" t="n">
         <f aca="false">IF(Z5&lt;&gt;CONCATENATE("Mtx",Y5),1,0)</f>
@@ -24344,10 +24341,10 @@
         <v>4</v>
       </c>
       <c r="AE5" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AF5" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG5" s="2" t="n">
         <f aca="false">IF(AE5&lt;&gt;CONCATENATE("StMtx",AD5),1,0)</f>
@@ -24357,10 +24354,10 @@
         <v>4</v>
       </c>
       <c r="AJ5" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AK5" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL5" s="2" t="n">
         <f aca="false">IF(AJ5&lt;&gt;CONCATENATE("Fx",AI5),1,0)</f>
@@ -24371,10 +24368,10 @@
         <v>4</v>
       </c>
       <c r="AO5" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AP5" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ5" s="2" t="n">
         <f aca="false">IF(AO5&lt;&gt;CONCATENATE("StFx",AN5),1,0)</f>
@@ -24385,29 +24382,29 @@
         <v>4</v>
       </c>
       <c r="AT5" s="31" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AU5" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW5" s="28" t="n">
         <v>4</v>
       </c>
       <c r="AX5" s="31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AY5" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ5" s="2"/>
       <c r="BA5" s="28" t="n">
         <v>4</v>
       </c>
       <c r="BB5" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BC5" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24415,19 +24412,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2" t="n">
         <f aca="false">IF(F6&lt;&gt;CONCATENATE("Aux",E6),1,0)</f>
@@ -24437,10 +24434,10 @@
         <v>5</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L6" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M6" s="2" t="n">
         <f aca="false">IF(K6&lt;&gt;CONCATENATE("STAux",J6),1,0)</f>
@@ -24478,10 +24475,10 @@
         <v>5</v>
       </c>
       <c r="Z6" s="31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AA6" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB6" s="2" t="n">
         <f aca="false">IF(Z6&lt;&gt;CONCATENATE("Mtx",Y6),1,0)</f>
@@ -24492,10 +24489,10 @@
         <v>5</v>
       </c>
       <c r="AE6" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AF6" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG6" s="2" t="n">
         <f aca="false">IF(AE6&lt;&gt;CONCATENATE("StMtx",AD6),1,0)</f>
@@ -24505,10 +24502,10 @@
         <v>5</v>
       </c>
       <c r="AJ6" s="31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK6" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL6" s="2" t="n">
         <f aca="false">IF(AJ6&lt;&gt;CONCATENATE("Fx",AI6),1,0)</f>
@@ -24519,10 +24516,10 @@
         <v>5</v>
       </c>
       <c r="AO6" s="31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AP6" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ6" s="2" t="n">
         <f aca="false">IF(AO6&lt;&gt;CONCATENATE("StFx",AN6),1,0)</f>
@@ -24533,29 +24530,29 @@
         <v>5</v>
       </c>
       <c r="AT6" s="31" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AU6" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW6" s="28" t="n">
         <v>5</v>
       </c>
       <c r="AX6" s="31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AY6" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ6" s="2"/>
       <c r="BA6" s="28" t="n">
         <v>5</v>
       </c>
       <c r="BB6" s="31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BC6" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24563,20 +24560,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="28" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H7" s="2" t="n">
         <f aca="false">IF(F7&lt;&gt;CONCATENATE("Aux",E7),1,0)</f>
@@ -24586,10 +24583,10 @@
         <v>6</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M7" s="2" t="n">
         <f aca="false">IF(K7&lt;&gt;CONCATENATE("STAux",J7),1,0)</f>
@@ -24627,10 +24624,10 @@
         <v>6</v>
       </c>
       <c r="Z7" s="31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AA7" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB7" s="2" t="n">
         <f aca="false">IF(Z7&lt;&gt;CONCATENATE("Mtx",Y7),1,0)</f>
@@ -24641,10 +24638,10 @@
         <v>6</v>
       </c>
       <c r="AE7" s="31" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AF7" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG7" s="2" t="n">
         <f aca="false">IF(AE7&lt;&gt;CONCATENATE("StMtx",AD7),1,0)</f>
@@ -24654,10 +24651,10 @@
         <v>6</v>
       </c>
       <c r="AJ7" s="31" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AK7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL7" s="2" t="n">
         <f aca="false">IF(AJ7&lt;&gt;CONCATENATE("Fx",AI7),1,0)</f>
@@ -24668,10 +24665,10 @@
         <v>6</v>
       </c>
       <c r="AO7" s="31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AP7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ7" s="2" t="n">
         <f aca="false">IF(AO7&lt;&gt;CONCATENATE("StFx",AN7),1,0)</f>
@@ -24682,29 +24679,29 @@
         <v>6</v>
       </c>
       <c r="AT7" s="31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AU7" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW7" s="28" t="n">
         <v>6</v>
       </c>
       <c r="AX7" s="31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AY7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ7" s="2"/>
       <c r="BA7" s="28" t="n">
         <v>6</v>
       </c>
       <c r="BB7" s="31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="BC7" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24712,19 +24709,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E8" s="28" t="n">
         <v>7</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8" s="2" t="n">
         <f aca="false">IF(F8&lt;&gt;CONCATENATE("Aux",E8),1,0)</f>
@@ -24734,10 +24731,10 @@
         <v>7</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M8" s="2" t="n">
         <f aca="false">IF(K8&lt;&gt;CONCATENATE("STAux",J8),1,0)</f>
@@ -24775,10 +24772,10 @@
         <v>7</v>
       </c>
       <c r="Z8" s="31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB8" s="2" t="n">
         <f aca="false">IF(Z8&lt;&gt;CONCATENATE("Mtx",Y8),1,0)</f>
@@ -24789,10 +24786,10 @@
         <v>7</v>
       </c>
       <c r="AE8" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF8" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG8" s="2" t="n">
         <f aca="false">IF(AE8&lt;&gt;CONCATENATE("StMtx",AD8),1,0)</f>
@@ -24802,10 +24799,10 @@
         <v>7</v>
       </c>
       <c r="AJ8" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL8" s="2" t="n">
         <f aca="false">IF(AJ8&lt;&gt;CONCATENATE("Fx",AI8),1,0)</f>
@@ -24816,10 +24813,10 @@
         <v>7</v>
       </c>
       <c r="AO8" s="31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AP8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ8" s="2" t="n">
         <f aca="false">IF(AO8&lt;&gt;CONCATENATE("StFx",AN8),1,0)</f>
@@ -24830,29 +24827,29 @@
         <v>7</v>
       </c>
       <c r="AT8" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AU8" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW8" s="28" t="n">
         <v>7</v>
       </c>
       <c r="AX8" s="31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AY8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ8" s="2"/>
       <c r="BA8" s="28" t="n">
         <v>7</v>
       </c>
       <c r="BB8" s="31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="BC8" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24860,19 +24857,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H9" s="2" t="n">
         <f aca="false">IF(F9&lt;&gt;CONCATENATE("Aux",E9),1,0)</f>
@@ -24882,10 +24879,10 @@
         <v>8</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M9" s="2" t="n">
         <f aca="false">IF(K9&lt;&gt;CONCATENATE("STAux",J9),1,0)</f>
@@ -24923,10 +24920,10 @@
         <v>8</v>
       </c>
       <c r="Z9" s="31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB9" s="2" t="n">
         <f aca="false">IF(Z9&lt;&gt;CONCATENATE("Mtx",Y9),1,0)</f>
@@ -24937,10 +24934,10 @@
         <v>8</v>
       </c>
       <c r="AE9" s="31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF9" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG9" s="2" t="n">
         <f aca="false">IF(AE9&lt;&gt;CONCATENATE("StMtx",AD9),1,0)</f>
@@ -24950,10 +24947,10 @@
         <v>8</v>
       </c>
       <c r="AJ9" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AK9" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL9" s="2" t="n">
         <f aca="false">IF(AJ9&lt;&gt;CONCATENATE("Fx",AI9),1,0)</f>
@@ -24964,10 +24961,10 @@
         <v>8</v>
       </c>
       <c r="AO9" s="31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AP9" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ9" s="2" t="n">
         <f aca="false">IF(AO9&lt;&gt;CONCATENATE("StFx",AN9),1,0)</f>
@@ -24978,29 +24975,29 @@
         <v>8</v>
       </c>
       <c r="AT9" s="31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU9" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW9" s="28" t="n">
         <v>8</v>
       </c>
       <c r="AX9" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AY9" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AZ9" s="2"/>
       <c r="BA9" s="28" t="n">
         <v>8</v>
       </c>
       <c r="BB9" s="31" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="BC9" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25008,19 +25005,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10" s="28" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H10" s="2" t="n">
         <f aca="false">IF(F10&lt;&gt;CONCATENATE("Aux",E10),1,0)</f>
@@ -25030,10 +25027,10 @@
         <v>9</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L10" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M10" s="2" t="n">
         <f aca="false">IF(K10&lt;&gt;CONCATENATE("STAux",J10),1,0)</f>
@@ -25071,10 +25068,10 @@
         <v>9</v>
       </c>
       <c r="Z10" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB10" s="2" t="n">
         <f aca="false">IF(Z10&lt;&gt;CONCATENATE("Mtx",Y10),1,0)</f>
@@ -25085,10 +25082,10 @@
         <v>9</v>
       </c>
       <c r="AE10" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AF10" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG10" s="2" t="n">
         <f aca="false">IF(AE10&lt;&gt;CONCATENATE("StMtx",AD10),1,0)</f>
@@ -25098,10 +25095,10 @@
         <v>9</v>
       </c>
       <c r="AJ10" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AK10" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL10" s="2" t="n">
         <f aca="false">IF(AJ10&lt;&gt;CONCATENATE("Fx",AI10),1,0)</f>
@@ -25112,10 +25109,10 @@
         <v>9</v>
       </c>
       <c r="AO10" s="31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AP10" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ10" s="2" t="n">
         <f aca="false">IF(AO10&lt;&gt;CONCATENATE("StFx",AN10),1,0)</f>
@@ -25126,10 +25123,10 @@
         <v>9</v>
       </c>
       <c r="AT10" s="31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AU10" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25137,19 +25134,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>10</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H11" s="2" t="n">
         <f aca="false">IF(F11&lt;&gt;CONCATENATE("Aux",E11),1,0)</f>
@@ -25159,10 +25156,10 @@
         <v>10</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L11" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M11" s="2" t="n">
         <f aca="false">IF(K11&lt;&gt;CONCATENATE("STAux",J11),1,0)</f>
@@ -25200,10 +25197,10 @@
         <v>10</v>
       </c>
       <c r="Z11" s="31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB11" s="2" t="n">
         <f aca="false">IF(Z11&lt;&gt;CONCATENATE("Mtx",Y11),1,0)</f>
@@ -25214,10 +25211,10 @@
         <v>10</v>
       </c>
       <c r="AE11" s="31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AF11" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG11" s="2" t="n">
         <f aca="false">IF(AE11&lt;&gt;CONCATENATE("StMtx",AD11),1,0)</f>
@@ -25227,10 +25224,10 @@
         <v>10</v>
       </c>
       <c r="AJ11" s="31" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AK11" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL11" s="2" t="n">
         <f aca="false">IF(AJ11&lt;&gt;CONCATENATE("Fx",AI11),1,0)</f>
@@ -25241,10 +25238,10 @@
         <v>10</v>
       </c>
       <c r="AO11" s="31" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AP11" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ11" s="2" t="n">
         <f aca="false">IF(AO11&lt;&gt;CONCATENATE("StFx",AN11),1,0)</f>
@@ -25255,10 +25252,10 @@
         <v>10</v>
       </c>
       <c r="AT11" s="31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AU11" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25266,19 +25263,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="28" t="n">
         <v>11</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H12" s="2" t="n">
         <f aca="false">IF(F12&lt;&gt;CONCATENATE("Aux",E12),1,0)</f>
@@ -25288,10 +25285,10 @@
         <v>11</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L12" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M12" s="2" t="n">
         <f aca="false">IF(K12&lt;&gt;CONCATENATE("STAux",J12),1,0)</f>
@@ -25329,10 +25326,10 @@
         <v>11</v>
       </c>
       <c r="Z12" s="31" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB12" s="2" t="n">
         <f aca="false">IF(Z12&lt;&gt;CONCATENATE("Mtx",Y12),1,0)</f>
@@ -25343,10 +25340,10 @@
         <v>11</v>
       </c>
       <c r="AE12" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AF12" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG12" s="2" t="n">
         <f aca="false">IF(AE12&lt;&gt;CONCATENATE("StMtx",AD12),1,0)</f>
@@ -25356,10 +25353,10 @@
         <v>11</v>
       </c>
       <c r="AJ12" s="31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AK12" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL12" s="2" t="n">
         <f aca="false">IF(AJ12&lt;&gt;CONCATENATE("Fx",AI12),1,0)</f>
@@ -25370,10 +25367,10 @@
         <v>11</v>
       </c>
       <c r="AO12" s="31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AP12" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ12" s="2" t="n">
         <f aca="false">IF(AO12&lt;&gt;CONCATENATE("StFx",AN12),1,0)</f>
@@ -25384,10 +25381,10 @@
         <v>11</v>
       </c>
       <c r="AT12" s="31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AU12" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25395,19 +25392,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>12</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H13" s="2" t="n">
         <f aca="false">IF(F13&lt;&gt;CONCATENATE("Aux",E13),1,0)</f>
@@ -25417,10 +25414,10 @@
         <v>12</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L13" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M13" s="2" t="n">
         <f aca="false">IF(K13&lt;&gt;CONCATENATE("STAux",J13),1,0)</f>
@@ -25458,10 +25455,10 @@
         <v>12</v>
       </c>
       <c r="Z13" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB13" s="2" t="n">
         <f aca="false">IF(Z13&lt;&gt;CONCATENATE("Mtx",Y13),1,0)</f>
@@ -25472,10 +25469,10 @@
         <v>12</v>
       </c>
       <c r="AE13" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AF13" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG13" s="2" t="n">
         <f aca="false">IF(AE13&lt;&gt;CONCATENATE("StMtx",AD13),1,0)</f>
@@ -25485,10 +25482,10 @@
         <v>12</v>
       </c>
       <c r="AJ13" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AK13" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL13" s="2" t="n">
         <f aca="false">IF(AJ13&lt;&gt;CONCATENATE("Fx",AI13),1,0)</f>
@@ -25499,10 +25496,10 @@
         <v>12</v>
       </c>
       <c r="AO13" s="31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AP13" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ13" s="2" t="n">
         <f aca="false">IF(AO13&lt;&gt;CONCATENATE("StFx",AN13),1,0)</f>
@@ -25513,10 +25510,10 @@
         <v>12</v>
       </c>
       <c r="AT13" s="31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AU13" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25524,19 +25521,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14" s="28" t="n">
         <v>13</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H14" s="2" t="n">
         <f aca="false">IF(F14&lt;&gt;CONCATENATE("Aux",E14),1,0)</f>
@@ -25546,10 +25543,10 @@
         <v>13</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L14" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M14" s="2" t="n">
         <f aca="false">IF(K14&lt;&gt;CONCATENATE("STAux",J14),1,0)</f>
@@ -25560,7 +25557,7 @@
         <v>13</v>
       </c>
       <c r="P14" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q14" s="30" t="s">
         <v>75</v>
@@ -25574,7 +25571,7 @@
         <v>13</v>
       </c>
       <c r="U14" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="V14" s="30" t="s">
         <v>75</v>
@@ -25587,10 +25584,10 @@
         <v>13</v>
       </c>
       <c r="Z14" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB14" s="2" t="n">
         <f aca="false">IF(Z14&lt;&gt;CONCATENATE("Mtx",Y14),1,0)</f>
@@ -25601,10 +25598,10 @@
         <v>13</v>
       </c>
       <c r="AE14" s="31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AF14" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG14" s="2" t="n">
         <f aca="false">IF(AE14&lt;&gt;CONCATENATE("StMtx",AD14),1,0)</f>
@@ -25614,10 +25611,10 @@
         <v>13</v>
       </c>
       <c r="AJ14" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AK14" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL14" s="2" t="n">
         <f aca="false">IF(AJ14&lt;&gt;CONCATENATE("Fx",AI14),1,0)</f>
@@ -25628,10 +25625,10 @@
         <v>13</v>
       </c>
       <c r="AO14" s="31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AP14" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ14" s="2" t="n">
         <f aca="false">IF(AO14&lt;&gt;CONCATENATE("StFx",AN14),1,0)</f>
@@ -25642,10 +25639,10 @@
         <v>13</v>
       </c>
       <c r="AT14" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AU14" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25653,19 +25650,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>14</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H15" s="2" t="n">
         <f aca="false">IF(F15&lt;&gt;CONCATENATE("Aux",E15),1,0)</f>
@@ -25675,10 +25672,10 @@
         <v>14</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L15" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M15" s="2" t="n">
         <f aca="false">IF(K15&lt;&gt;CONCATENATE("STAux",J15),1,0)</f>
@@ -25689,7 +25686,7 @@
         <v>14</v>
       </c>
       <c r="P15" s="31" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q15" s="30" t="s">
         <v>75</v>
@@ -25703,7 +25700,7 @@
         <v>14</v>
       </c>
       <c r="U15" s="31" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V15" s="30" t="s">
         <v>75</v>
@@ -25716,10 +25713,10 @@
         <v>14</v>
       </c>
       <c r="Z15" s="31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB15" s="2" t="n">
         <f aca="false">IF(Z15&lt;&gt;CONCATENATE("Mtx",Y15),1,0)</f>
@@ -25730,10 +25727,10 @@
         <v>14</v>
       </c>
       <c r="AE15" s="31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AF15" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG15" s="2" t="n">
         <f aca="false">IF(AE15&lt;&gt;CONCATENATE("StMtx",AD15),1,0)</f>
@@ -25743,10 +25740,10 @@
         <v>14</v>
       </c>
       <c r="AJ15" s="31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK15" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL15" s="2" t="n">
         <f aca="false">IF(AJ15&lt;&gt;CONCATENATE("Fx",AI15),1,0)</f>
@@ -25757,10 +25754,10 @@
         <v>14</v>
       </c>
       <c r="AO15" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AP15" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ15" s="2" t="n">
         <f aca="false">IF(AO15&lt;&gt;CONCATENATE("StFx",AN15),1,0)</f>
@@ -25771,10 +25768,10 @@
         <v>14</v>
       </c>
       <c r="AT15" s="31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AU15" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25782,19 +25779,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E16" s="28" t="n">
         <v>15</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H16" s="2" t="n">
         <f aca="false">IF(F16&lt;&gt;CONCATENATE("Aux",E16),1,0)</f>
@@ -25804,10 +25801,10 @@
         <v>15</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L16" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M16" s="2" t="n">
         <f aca="false">IF(K16&lt;&gt;CONCATENATE("STAux",J16),1,0)</f>
@@ -25818,7 +25815,7 @@
         <v>15</v>
       </c>
       <c r="P16" s="31" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q16" s="30" t="s">
         <v>75</v>
@@ -25832,7 +25829,7 @@
         <v>15</v>
       </c>
       <c r="U16" s="31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="V16" s="30" t="s">
         <v>75</v>
@@ -25845,10 +25842,10 @@
         <v>15</v>
       </c>
       <c r="Z16" s="31" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB16" s="2" t="n">
         <f aca="false">IF(Z16&lt;&gt;CONCATENATE("Mtx",Y16),1,0)</f>
@@ -25859,10 +25856,10 @@
         <v>15</v>
       </c>
       <c r="AE16" s="31" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AF16" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG16" s="2" t="n">
         <f aca="false">IF(AE16&lt;&gt;CONCATENATE("StMtx",AD16),1,0)</f>
@@ -25872,10 +25869,10 @@
         <v>15</v>
       </c>
       <c r="AJ16" s="31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AK16" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL16" s="2" t="n">
         <f aca="false">IF(AJ16&lt;&gt;CONCATENATE("Fx",AI16),1,0)</f>
@@ -25886,10 +25883,10 @@
         <v>15</v>
       </c>
       <c r="AO16" s="31" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AP16" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ16" s="2" t="n">
         <f aca="false">IF(AO16&lt;&gt;CONCATENATE("StFx",AN16),1,0)</f>
@@ -25900,10 +25897,10 @@
         <v>15</v>
       </c>
       <c r="AT16" s="31" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AU16" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25911,19 +25908,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17" s="28" t="n">
         <v>16</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G17" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H17" s="2" t="n">
         <f aca="false">IF(F17&lt;&gt;CONCATENATE("Aux",E17),1,0)</f>
@@ -25933,10 +25930,10 @@
         <v>16</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L17" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M17" s="2" t="n">
         <f aca="false">IF(K17&lt;&gt;CONCATENATE("STAux",J17),1,0)</f>
@@ -25947,7 +25944,7 @@
         <v>16</v>
       </c>
       <c r="P17" s="31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q17" s="30" t="s">
         <v>75</v>
@@ -25961,7 +25958,7 @@
         <v>16</v>
       </c>
       <c r="U17" s="31" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="V17" s="30" t="s">
         <v>75</v>
@@ -25974,10 +25971,10 @@
         <v>16</v>
       </c>
       <c r="Z17" s="31" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB17" s="2" t="n">
         <f aca="false">IF(Z17&lt;&gt;CONCATENATE("Mtx",Y17),1,0)</f>
@@ -25988,10 +25985,10 @@
         <v>16</v>
       </c>
       <c r="AE17" s="31" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AF17" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG17" s="2" t="n">
         <f aca="false">IF(AE17&lt;&gt;CONCATENATE("StMtx",AD17),1,0)</f>
@@ -26001,10 +25998,10 @@
         <v>16</v>
       </c>
       <c r="AJ17" s="31" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AK17" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL17" s="2" t="n">
         <f aca="false">IF(AJ17&lt;&gt;CONCATENATE("Fx",AI17),1,0)</f>
@@ -26015,10 +26012,10 @@
         <v>16</v>
       </c>
       <c r="AO17" s="31" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AP17" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ17" s="2" t="n">
         <f aca="false">IF(AO17&lt;&gt;CONCATENATE("StFx",AN17),1,0)</f>
@@ -26029,10 +26026,10 @@
         <v>16</v>
       </c>
       <c r="AT17" s="31" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AU17" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26040,19 +26037,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" s="28" t="n">
         <v>17</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H18" s="2" t="n">
         <f aca="false">IF(F18&lt;&gt;CONCATENATE("Aux",E18),1,0)</f>
@@ -26062,10 +26059,10 @@
         <v>17</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L18" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M18" s="2" t="n">
         <f aca="false">IF(K18&lt;&gt;CONCATENATE("STAux",J18),1,0)</f>
@@ -26076,7 +26073,7 @@
         <v>17</v>
       </c>
       <c r="P18" s="31" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q18" s="30" t="s">
         <v>75</v>
@@ -26090,7 +26087,7 @@
         <v>17</v>
       </c>
       <c r="U18" s="31" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="V18" s="30" t="s">
         <v>75</v>
@@ -26103,10 +26100,10 @@
         <v>17</v>
       </c>
       <c r="Z18" s="31" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB18" s="2" t="n">
         <f aca="false">IF(Z18&lt;&gt;CONCATENATE("Mtx",Y18),1,0)</f>
@@ -26117,10 +26114,10 @@
         <v>17</v>
       </c>
       <c r="AE18" s="31" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AF18" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG18" s="2" t="n">
         <f aca="false">IF(AE18&lt;&gt;CONCATENATE("StMtx",AD18),1,0)</f>
@@ -26132,19 +26129,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" s="28" t="n">
         <v>18</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G19" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H19" s="2" t="n">
         <f aca="false">IF(F19&lt;&gt;CONCATENATE("Aux",E19),1,0)</f>
@@ -26154,10 +26151,10 @@
         <v>18</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L19" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M19" s="2" t="n">
         <f aca="false">IF(K19&lt;&gt;CONCATENATE("STAux",J19),1,0)</f>
@@ -26168,7 +26165,7 @@
         <v>18</v>
       </c>
       <c r="P19" s="31" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q19" s="30" t="s">
         <v>75</v>
@@ -26182,7 +26179,7 @@
         <v>18</v>
       </c>
       <c r="U19" s="31" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="V19" s="30" t="s">
         <v>75</v>
@@ -26195,10 +26192,10 @@
         <v>18</v>
       </c>
       <c r="Z19" s="31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB19" s="2" t="n">
         <f aca="false">IF(Z19&lt;&gt;CONCATENATE("Mtx",Y19),1,0)</f>
@@ -26209,10 +26206,10 @@
         <v>18</v>
       </c>
       <c r="AE19" s="31" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF19" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG19" s="2" t="n">
         <f aca="false">IF(AE19&lt;&gt;CONCATENATE("StMtx",AD19),1,0)</f>
@@ -26224,19 +26221,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20" s="28" t="n">
         <v>19</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H20" s="2" t="n">
         <f aca="false">IF(F20&lt;&gt;CONCATENATE("Aux",E20),1,0)</f>
@@ -26246,10 +26243,10 @@
         <v>19</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L20" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M20" s="2" t="n">
         <f aca="false">IF(K20&lt;&gt;CONCATENATE("STAux",J20),1,0)</f>
@@ -26260,7 +26257,7 @@
         <v>19</v>
       </c>
       <c r="P20" s="31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q20" s="30" t="s">
         <v>75</v>
@@ -26274,7 +26271,7 @@
         <v>19</v>
       </c>
       <c r="U20" s="31" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="V20" s="30" t="s">
         <v>75</v>
@@ -26287,10 +26284,10 @@
         <v>19</v>
       </c>
       <c r="Z20" s="31" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB20" s="2" t="n">
         <f aca="false">IF(Z20&lt;&gt;CONCATENATE("Mtx",Y20),1,0)</f>
@@ -26301,10 +26298,10 @@
         <v>19</v>
       </c>
       <c r="AE20" s="31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AF20" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG20" s="2" t="n">
         <f aca="false">IF(AE20&lt;&gt;CONCATENATE("StMtx",AD20),1,0)</f>
@@ -26316,19 +26313,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="28" t="n">
         <v>20</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G21" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2" t="n">
         <f aca="false">IF(F21&lt;&gt;CONCATENATE("Aux",E21),1,0)</f>
@@ -26338,10 +26335,10 @@
         <v>20</v>
       </c>
       <c r="K21" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L21" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M21" s="2" t="n">
         <f aca="false">IF(K21&lt;&gt;CONCATENATE("STAux",J21),1,0)</f>
@@ -26352,7 +26349,7 @@
         <v>20</v>
       </c>
       <c r="P21" s="31" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q21" s="30" t="s">
         <v>75</v>
@@ -26366,7 +26363,7 @@
         <v>20</v>
       </c>
       <c r="U21" s="31" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V21" s="30" t="s">
         <v>75</v>
@@ -26379,10 +26376,10 @@
         <v>20</v>
       </c>
       <c r="Z21" s="31" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB21" s="2" t="n">
         <f aca="false">IF(Z21&lt;&gt;CONCATENATE("Mtx",Y21),1,0)</f>
@@ -26393,10 +26390,10 @@
         <v>20</v>
       </c>
       <c r="AE21" s="31" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AF21" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG21" s="2" t="n">
         <f aca="false">IF(AE21&lt;&gt;CONCATENATE("StMtx",AD21),1,0)</f>
@@ -26408,19 +26405,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="28" t="n">
         <v>21</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G22" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="n">
         <f aca="false">IF(F22&lt;&gt;CONCATENATE("Aux",E22),1,0)</f>
@@ -26430,10 +26427,10 @@
         <v>21</v>
       </c>
       <c r="K22" s="31" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L22" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M22" s="2" t="n">
         <f aca="false">IF(K22&lt;&gt;CONCATENATE("STAux",J22),1,0)</f>
@@ -26444,7 +26441,7 @@
         <v>21</v>
       </c>
       <c r="P22" s="31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q22" s="30" t="s">
         <v>75</v>
@@ -26458,7 +26455,7 @@
         <v>21</v>
       </c>
       <c r="U22" s="31" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="V22" s="30" t="s">
         <v>75</v>
@@ -26471,10 +26468,10 @@
         <v>21</v>
       </c>
       <c r="Z22" s="31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB22" s="2" t="n">
         <f aca="false">IF(Z22&lt;&gt;CONCATENATE("Mtx",Y22),1,0)</f>
@@ -26485,10 +26482,10 @@
         <v>21</v>
       </c>
       <c r="AE22" s="31" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AF22" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG22" s="2" t="n">
         <f aca="false">IF(AE22&lt;&gt;CONCATENATE("StMtx",AD22),1,0)</f>
@@ -26500,19 +26497,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="28" t="n">
         <v>22</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G23" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H23" s="2" t="n">
         <f aca="false">IF(F23&lt;&gt;CONCATENATE("Aux",E23),1,0)</f>
@@ -26522,10 +26519,10 @@
         <v>22</v>
       </c>
       <c r="K23" s="31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L23" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M23" s="2" t="n">
         <f aca="false">IF(K23&lt;&gt;CONCATENATE("STAux",J23),1,0)</f>
@@ -26536,7 +26533,7 @@
         <v>22</v>
       </c>
       <c r="P23" s="31" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q23" s="30" t="s">
         <v>75</v>
@@ -26550,7 +26547,7 @@
         <v>22</v>
       </c>
       <c r="U23" s="31" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="V23" s="30" t="s">
         <v>75</v>
@@ -26563,10 +26560,10 @@
         <v>22</v>
       </c>
       <c r="Z23" s="31" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB23" s="2" t="n">
         <f aca="false">IF(Z23&lt;&gt;CONCATENATE("Mtx",Y23),1,0)</f>
@@ -26577,10 +26574,10 @@
         <v>22</v>
       </c>
       <c r="AE23" s="31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AF23" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG23" s="2" t="n">
         <f aca="false">IF(AE23&lt;&gt;CONCATENATE("StMtx",AD23),1,0)</f>
@@ -26592,19 +26589,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E24" s="28" t="n">
         <v>23</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2" t="n">
         <f aca="false">IF(F24&lt;&gt;CONCATENATE("Aux",E24),1,0)</f>
@@ -26614,10 +26611,10 @@
         <v>23</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L24" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M24" s="2" t="n">
         <f aca="false">IF(K24&lt;&gt;CONCATENATE("STAux",J24),1,0)</f>
@@ -26628,7 +26625,7 @@
         <v>23</v>
       </c>
       <c r="P24" s="31" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q24" s="30" t="s">
         <v>75</v>
@@ -26642,7 +26639,7 @@
         <v>23</v>
       </c>
       <c r="U24" s="31" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="V24" s="30" t="s">
         <v>75</v>
@@ -26655,10 +26652,10 @@
         <v>23</v>
       </c>
       <c r="Z24" s="31" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB24" s="2" t="n">
         <f aca="false">IF(Z24&lt;&gt;CONCATENATE("Mtx",Y24),1,0)</f>
@@ -26669,10 +26666,10 @@
         <v>23</v>
       </c>
       <c r="AE24" s="31" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AF24" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG24" s="2" t="n">
         <f aca="false">IF(AE24&lt;&gt;CONCATENATE("StMtx",AD24),1,0)</f>
@@ -26684,19 +26681,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" s="28" t="n">
         <v>24</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G25" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H25" s="2" t="n">
         <f aca="false">IF(F25&lt;&gt;CONCATENATE("Aux",E25),1,0)</f>
@@ -26706,10 +26703,10 @@
         <v>24</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L25" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M25" s="2" t="n">
         <f aca="false">IF(K25&lt;&gt;CONCATENATE("STAux",J25),1,0)</f>
@@ -26720,7 +26717,7 @@
         <v>24</v>
       </c>
       <c r="P25" s="31" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q25" s="30" t="s">
         <v>75</v>
@@ -26734,7 +26731,7 @@
         <v>24</v>
       </c>
       <c r="U25" s="31" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="V25" s="30" t="s">
         <v>75</v>
@@ -26747,10 +26744,10 @@
         <v>24</v>
       </c>
       <c r="Z25" s="31" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA25" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB25" s="2" t="n">
         <f aca="false">IF(Z25&lt;&gt;CONCATENATE("Mtx",Y25),1,0)</f>
@@ -26761,10 +26758,10 @@
         <v>24</v>
       </c>
       <c r="AE25" s="31" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AF25" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG25" s="2" t="n">
         <f aca="false">IF(AE25&lt;&gt;CONCATENATE("StMtx",AD25),1,0)</f>
@@ -26776,10 +26773,10 @@
         <v>25</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H26" s="2" t="n">
         <f aca="false">IF(F26&lt;&gt;CONCATENATE("Aux",E26),1,0)</f>
@@ -26789,10 +26786,10 @@
         <v>25</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L26" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M26" s="2" t="n">
         <f aca="false">IF(K26&lt;&gt;CONCATENATE("STAux",J26),1,0)</f>
@@ -26803,7 +26800,7 @@
         <v>25</v>
       </c>
       <c r="P26" s="31" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q26" s="30" t="s">
         <v>75</v>
@@ -26817,7 +26814,7 @@
         <v>25</v>
       </c>
       <c r="U26" s="31" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="V26" s="30" t="s">
         <v>75</v>
@@ -26830,10 +26827,10 @@
         <v>25</v>
       </c>
       <c r="Z26" s="31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AA26" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB26" s="2" t="n">
         <f aca="false">IF(Z26&lt;&gt;CONCATENATE("Mtx",Y26),1,0)</f>
@@ -26844,10 +26841,10 @@
         <v>25</v>
       </c>
       <c r="AE26" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AF26" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG26" s="2" t="n">
         <f aca="false">IF(AE26&lt;&gt;CONCATENATE("StMtx",AD26),1,0)</f>
@@ -26859,10 +26856,10 @@
         <v>26</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2" t="n">
         <f aca="false">IF(F27&lt;&gt;CONCATENATE("Aux",E27),1,0)</f>
@@ -26872,10 +26869,10 @@
         <v>26</v>
       </c>
       <c r="K27" s="31" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L27" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M27" s="2" t="n">
         <f aca="false">IF(K27&lt;&gt;CONCATENATE("STAux",J27),1,0)</f>
@@ -26886,7 +26883,7 @@
         <v>26</v>
       </c>
       <c r="P27" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q27" s="30" t="s">
         <v>75</v>
@@ -26900,7 +26897,7 @@
         <v>26</v>
       </c>
       <c r="U27" s="31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="V27" s="30" t="s">
         <v>75</v>
@@ -26913,10 +26910,10 @@
         <v>26</v>
       </c>
       <c r="Z27" s="31" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA27" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB27" s="2" t="n">
         <f aca="false">IF(Z27&lt;&gt;CONCATENATE("Mtx",Y27),1,0)</f>
@@ -26927,10 +26924,10 @@
         <v>26</v>
       </c>
       <c r="AE27" s="31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AF27" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG27" s="2" t="n">
         <f aca="false">IF(AE27&lt;&gt;CONCATENATE("StMtx",AD27),1,0)</f>
@@ -26942,10 +26939,10 @@
         <v>27</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H28" s="2" t="n">
         <f aca="false">IF(F28&lt;&gt;CONCATENATE("Aux",E28),1,0)</f>
@@ -26955,10 +26952,10 @@
         <v>27</v>
       </c>
       <c r="K28" s="31" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L28" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M28" s="2" t="n">
         <f aca="false">IF(K28&lt;&gt;CONCATENATE("STAux",J28),1,0)</f>
@@ -26969,7 +26966,7 @@
         <v>27</v>
       </c>
       <c r="P28" s="31" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q28" s="30" t="s">
         <v>75</v>
@@ -26983,7 +26980,7 @@
         <v>27</v>
       </c>
       <c r="U28" s="31" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="V28" s="30" t="s">
         <v>75</v>
@@ -26996,10 +26993,10 @@
         <v>27</v>
       </c>
       <c r="Z28" s="31" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB28" s="2" t="n">
         <f aca="false">IF(Z28&lt;&gt;CONCATENATE("Mtx",Y28),1,0)</f>
@@ -27010,10 +27007,10 @@
         <v>27</v>
       </c>
       <c r="AE28" s="31" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AF28" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG28" s="2" t="n">
         <f aca="false">IF(AE28&lt;&gt;CONCATENATE("StMtx",AD28),1,0)</f>
@@ -27025,10 +27022,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H29" s="2" t="n">
         <f aca="false">IF(F29&lt;&gt;CONCATENATE("Aux",E29),1,0)</f>
@@ -27038,10 +27035,10 @@
         <v>28</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L29" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M29" s="2" t="n">
         <f aca="false">IF(K29&lt;&gt;CONCATENATE("STAux",J29),1,0)</f>
@@ -27052,7 +27049,7 @@
         <v>28</v>
       </c>
       <c r="P29" s="31" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q29" s="30" t="s">
         <v>75</v>
@@ -27066,7 +27063,7 @@
         <v>28</v>
       </c>
       <c r="U29" s="31" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="V29" s="30" t="s">
         <v>75</v>
@@ -27079,10 +27076,10 @@
         <v>28</v>
       </c>
       <c r="Z29" s="31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AA29" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB29" s="2" t="n">
         <f aca="false">IF(Z29&lt;&gt;CONCATENATE("Mtx",Y29),1,0)</f>
@@ -27093,10 +27090,10 @@
         <v>28</v>
       </c>
       <c r="AE29" s="31" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AF29" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG29" s="2" t="n">
         <f aca="false">IF(AE29&lt;&gt;CONCATENATE("StMtx",AD29),1,0)</f>
@@ -27108,10 +27105,10 @@
         <v>29</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H30" s="2" t="n">
         <f aca="false">IF(F30&lt;&gt;CONCATENATE("Aux",E30),1,0)</f>
@@ -27121,10 +27118,10 @@
         <v>29</v>
       </c>
       <c r="K30" s="31" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L30" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M30" s="2" t="n">
         <f aca="false">IF(K30&lt;&gt;CONCATENATE("STAux",J30),1,0)</f>
@@ -27135,7 +27132,7 @@
         <v>29</v>
       </c>
       <c r="P30" s="31" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q30" s="30" t="s">
         <v>75</v>
@@ -27149,7 +27146,7 @@
         <v>29</v>
       </c>
       <c r="U30" s="31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V30" s="30" t="s">
         <v>75</v>
@@ -27162,10 +27159,10 @@
         <v>29</v>
       </c>
       <c r="Z30" s="31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AA30" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB30" s="2" t="n">
         <f aca="false">IF(Z30&lt;&gt;CONCATENATE("Mtx",Y30),1,0)</f>
@@ -27176,10 +27173,10 @@
         <v>29</v>
       </c>
       <c r="AE30" s="31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AF30" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG30" s="2" t="n">
         <f aca="false">IF(AE30&lt;&gt;CONCATENATE("StMtx",AD30),1,0)</f>
@@ -27191,10 +27188,10 @@
         <v>30</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G31" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H31" s="2" t="n">
         <f aca="false">IF(F31&lt;&gt;CONCATENATE("Aux",E31),1,0)</f>
@@ -27204,10 +27201,10 @@
         <v>30</v>
       </c>
       <c r="K31" s="31" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L31" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M31" s="2" t="n">
         <f aca="false">IF(K31&lt;&gt;CONCATENATE("STAux",J31),1,0)</f>
@@ -27218,7 +27215,7 @@
         <v>30</v>
       </c>
       <c r="P31" s="31" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q31" s="30" t="s">
         <v>75</v>
@@ -27232,7 +27229,7 @@
         <v>30</v>
       </c>
       <c r="U31" s="31" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="V31" s="30" t="s">
         <v>75</v>
@@ -27245,10 +27242,10 @@
         <v>30</v>
       </c>
       <c r="Z31" s="31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AA31" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB31" s="2" t="n">
         <f aca="false">IF(Z31&lt;&gt;CONCATENATE("Mtx",Y31),1,0)</f>
@@ -27259,10 +27256,10 @@
         <v>30</v>
       </c>
       <c r="AE31" s="31" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF31" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG31" s="2" t="n">
         <f aca="false">IF(AE31&lt;&gt;CONCATENATE("StMtx",AD31),1,0)</f>
@@ -27274,10 +27271,10 @@
         <v>31</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G32" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H32" s="2" t="n">
         <f aca="false">IF(F32&lt;&gt;CONCATENATE("Aux",E32),1,0)</f>
@@ -27287,10 +27284,10 @@
         <v>31</v>
       </c>
       <c r="K32" s="31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L32" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M32" s="2" t="n">
         <f aca="false">IF(K32&lt;&gt;CONCATENATE("STAux",J32),1,0)</f>
@@ -27301,7 +27298,7 @@
         <v>31</v>
       </c>
       <c r="P32" s="31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q32" s="30" t="s">
         <v>75</v>
@@ -27315,7 +27312,7 @@
         <v>31</v>
       </c>
       <c r="U32" s="31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V32" s="30" t="s">
         <v>75</v>
@@ -27328,10 +27325,10 @@
         <v>31</v>
       </c>
       <c r="Z32" s="31" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AA32" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB32" s="2" t="n">
         <f aca="false">IF(Z32&lt;&gt;CONCATENATE("Mtx",Y32),1,0)</f>
@@ -27342,10 +27339,10 @@
         <v>31</v>
       </c>
       <c r="AE32" s="31" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AF32" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG32" s="2" t="n">
         <f aca="false">IF(AE32&lt;&gt;CONCATENATE("StMtx",AD32),1,0)</f>
@@ -27357,10 +27354,10 @@
         <v>32</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H33" s="2" t="n">
         <f aca="false">IF(F33&lt;&gt;CONCATENATE("Aux",E33),1,0)</f>
@@ -27371,7 +27368,7 @@
         <v>32</v>
       </c>
       <c r="P33" s="31" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q33" s="30" t="s">
         <v>75</v>
@@ -27386,10 +27383,10 @@
         <v>32</v>
       </c>
       <c r="Z33" s="31" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AA33" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB33" s="2" t="n">
         <f aca="false">IF(Z33&lt;&gt;CONCATENATE("Mtx",Y33),1,0)</f>
@@ -27403,10 +27400,10 @@
         <v>33</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G34" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H34" s="2" t="n">
         <f aca="false">IF(F34&lt;&gt;CONCATENATE("Aux",E34),1,0)</f>
@@ -27416,7 +27413,7 @@
         <v>33</v>
       </c>
       <c r="P34" s="31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q34" s="30" t="s">
         <v>75</v>
@@ -27430,10 +27427,10 @@
         <v>33</v>
       </c>
       <c r="Z34" s="31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA34" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB34" s="2" t="n">
         <f aca="false">IF(Z34&lt;&gt;CONCATENATE("Mtx",Y34),1,0)</f>
@@ -27447,10 +27444,10 @@
         <v>34</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G35" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H35" s="2" t="n">
         <f aca="false">IF(F35&lt;&gt;CONCATENATE("Aux",E35),1,0)</f>
@@ -27460,7 +27457,7 @@
         <v>34</v>
       </c>
       <c r="P35" s="31" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q35" s="30" t="s">
         <v>75</v>
@@ -27474,10 +27471,10 @@
         <v>34</v>
       </c>
       <c r="Z35" s="31" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AA35" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB35" s="2" t="n">
         <f aca="false">IF(Z35&lt;&gt;CONCATENATE("Mtx",Y35),1,0)</f>
@@ -27491,10 +27488,10 @@
         <v>35</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G36" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H36" s="2" t="n">
         <f aca="false">IF(F36&lt;&gt;CONCATENATE("Aux",E36),1,0)</f>
@@ -27504,7 +27501,7 @@
         <v>35</v>
       </c>
       <c r="P36" s="31" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q36" s="30" t="s">
         <v>75</v>
@@ -27518,10 +27515,10 @@
         <v>35</v>
       </c>
       <c r="Z36" s="31" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AA36" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB36" s="2" t="n">
         <f aca="false">IF(Z36&lt;&gt;CONCATENATE("Mtx",Y36),1,0)</f>
@@ -27534,10 +27531,10 @@
         <v>36</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G37" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H37" s="2" t="n">
         <f aca="false">IF(F37&lt;&gt;CONCATENATE("Aux",E37),1,0)</f>
@@ -27547,7 +27544,7 @@
         <v>36</v>
       </c>
       <c r="P37" s="31" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q37" s="30" t="s">
         <v>75</v>
@@ -27561,10 +27558,10 @@
         <v>36</v>
       </c>
       <c r="Z37" s="31" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AA37" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB37" s="2" t="n">
         <f aca="false">IF(Z37&lt;&gt;CONCATENATE("Mtx",Y37),1,0)</f>
@@ -27577,10 +27574,10 @@
         <v>37</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G38" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H38" s="2" t="n">
         <f aca="false">IF(F38&lt;&gt;CONCATENATE("Aux",E38),1,0)</f>
@@ -27590,7 +27587,7 @@
         <v>37</v>
       </c>
       <c r="P38" s="31" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q38" s="30" t="s">
         <v>75</v>
@@ -27604,10 +27601,10 @@
         <v>37</v>
       </c>
       <c r="Z38" s="31" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA38" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB38" s="2" t="n">
         <f aca="false">IF(Z38&lt;&gt;CONCATENATE("Mtx",Y38),1,0)</f>
@@ -27620,10 +27617,10 @@
         <v>38</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H39" s="2" t="n">
         <f aca="false">IF(F39&lt;&gt;CONCATENATE("Aux",E39),1,0)</f>
@@ -27633,7 +27630,7 @@
         <v>38</v>
       </c>
       <c r="P39" s="31" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q39" s="30" t="s">
         <v>75</v>
@@ -27647,10 +27644,10 @@
         <v>38</v>
       </c>
       <c r="Z39" s="31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AA39" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB39" s="2" t="n">
         <f aca="false">IF(Z39&lt;&gt;CONCATENATE("Mtx",Y39),1,0)</f>
@@ -27663,10 +27660,10 @@
         <v>39</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G40" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H40" s="2" t="n">
         <f aca="false">IF(F40&lt;&gt;CONCATENATE("Aux",E40),1,0)</f>
@@ -27676,7 +27673,7 @@
         <v>39</v>
       </c>
       <c r="P40" s="31" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q40" s="30" t="s">
         <v>75</v>
@@ -27690,10 +27687,10 @@
         <v>39</v>
       </c>
       <c r="Z40" s="31" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AA40" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB40" s="2" t="n">
         <f aca="false">IF(Z40&lt;&gt;CONCATENATE("Mtx",Y40),1,0)</f>
@@ -27706,10 +27703,10 @@
         <v>40</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G41" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H41" s="2" t="n">
         <f aca="false">IF(F41&lt;&gt;CONCATENATE("Aux",E41),1,0)</f>
@@ -27719,7 +27716,7 @@
         <v>40</v>
       </c>
       <c r="P41" s="31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q41" s="30" t="s">
         <v>75</v>
@@ -27733,10 +27730,10 @@
         <v>40</v>
       </c>
       <c r="Z41" s="31" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AA41" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB41" s="2" t="n">
         <f aca="false">IF(Z41&lt;&gt;CONCATENATE("Mtx",Y41),1,0)</f>
@@ -27749,10 +27746,10 @@
         <v>41</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G42" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H42" s="2" t="n">
         <f aca="false">IF(F42&lt;&gt;CONCATENATE("Aux",E42),1,0)</f>
@@ -27762,7 +27759,7 @@
         <v>41</v>
       </c>
       <c r="P42" s="31" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q42" s="30" t="s">
         <v>75</v>
@@ -27776,10 +27773,10 @@
         <v>41</v>
       </c>
       <c r="Z42" s="31" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA42" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB42" s="2" t="n">
         <f aca="false">IF(Z42&lt;&gt;CONCATENATE("Mtx",Y42),1,0)</f>
@@ -27792,10 +27789,10 @@
         <v>42</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G43" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H43" s="2" t="n">
         <f aca="false">IF(F43&lt;&gt;CONCATENATE("Aux",E43),1,0)</f>
@@ -27805,7 +27802,7 @@
         <v>42</v>
       </c>
       <c r="P43" s="31" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q43" s="30" t="s">
         <v>75</v>
@@ -27819,10 +27816,10 @@
         <v>42</v>
       </c>
       <c r="Z43" s="31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AA43" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB43" s="2" t="n">
         <f aca="false">IF(Z43&lt;&gt;CONCATENATE("Mtx",Y43),1,0)</f>
@@ -27835,10 +27832,10 @@
         <v>43</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G44" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H44" s="2" t="n">
         <f aca="false">IF(F44&lt;&gt;CONCATENATE("Aux",E44),1,0)</f>
@@ -27848,7 +27845,7 @@
         <v>43</v>
       </c>
       <c r="P44" s="31" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q44" s="30" t="s">
         <v>75</v>
@@ -27862,10 +27859,10 @@
         <v>43</v>
       </c>
       <c r="Z44" s="31" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AA44" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB44" s="2" t="n">
         <f aca="false">IF(Z44&lt;&gt;CONCATENATE("Mtx",Y44),1,0)</f>
@@ -27878,10 +27875,10 @@
         <v>44</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G45" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H45" s="2" t="n">
         <f aca="false">IF(F45&lt;&gt;CONCATENATE("Aux",E45),1,0)</f>
@@ -27891,7 +27888,7 @@
         <v>44</v>
       </c>
       <c r="P45" s="31" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Q45" s="30" t="s">
         <v>75</v>
@@ -27905,10 +27902,10 @@
         <v>44</v>
       </c>
       <c r="Z45" s="31" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AA45" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB45" s="2" t="n">
         <f aca="false">IF(Z45&lt;&gt;CONCATENATE("Mtx",Y45),1,0)</f>
@@ -27921,10 +27918,10 @@
         <v>45</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G46" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H46" s="2" t="n">
         <f aca="false">IF(F46&lt;&gt;CONCATENATE("Aux",E46),1,0)</f>
@@ -27934,7 +27931,7 @@
         <v>45</v>
       </c>
       <c r="P46" s="31" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q46" s="30" t="s">
         <v>75</v>
@@ -27948,10 +27945,10 @@
         <v>45</v>
       </c>
       <c r="Z46" s="31" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AA46" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB46" s="2" t="n">
         <f aca="false">IF(Z46&lt;&gt;CONCATENATE("Mtx",Y46),1,0)</f>
@@ -27964,10 +27961,10 @@
         <v>46</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G47" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H47" s="2" t="n">
         <f aca="false">IF(F47&lt;&gt;CONCATENATE("Aux",E47),1,0)</f>
@@ -27977,7 +27974,7 @@
         <v>46</v>
       </c>
       <c r="P47" s="31" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q47" s="30" t="s">
         <v>75</v>
@@ -27991,10 +27988,10 @@
         <v>46</v>
       </c>
       <c r="Z47" s="31" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AA47" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB47" s="2" t="n">
         <f aca="false">IF(Z47&lt;&gt;CONCATENATE("Mtx",Y47),1,0)</f>
@@ -28007,10 +28004,10 @@
         <v>47</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G48" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H48" s="2" t="n">
         <f aca="false">IF(F48&lt;&gt;CONCATENATE("Aux",E48),1,0)</f>
@@ -28020,7 +28017,7 @@
         <v>47</v>
       </c>
       <c r="P48" s="31" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q48" s="30" t="s">
         <v>75</v>
@@ -28034,10 +28031,10 @@
         <v>47</v>
       </c>
       <c r="Z48" s="31" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AA48" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB48" s="2" t="n">
         <f aca="false">IF(Z48&lt;&gt;CONCATENATE("Mtx",Y48),1,0)</f>
@@ -28050,10 +28047,10 @@
         <v>48</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G49" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H49" s="2" t="n">
         <f aca="false">IF(F49&lt;&gt;CONCATENATE("Aux",E49),1,0)</f>
@@ -28063,7 +28060,7 @@
         <v>48</v>
       </c>
       <c r="P49" s="31" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q49" s="30" t="s">
         <v>75</v>
@@ -28077,10 +28074,10 @@
         <v>48</v>
       </c>
       <c r="Z49" s="31" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AA49" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB49" s="2" t="n">
         <f aca="false">IF(Z49&lt;&gt;CONCATENATE("Mtx",Y49),1,0)</f>
@@ -28093,10 +28090,10 @@
         <v>49</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G50" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H50" s="2" t="n">
         <f aca="false">IF(F50&lt;&gt;CONCATENATE("Aux",E50),1,0)</f>
@@ -28106,7 +28103,7 @@
         <v>49</v>
       </c>
       <c r="P50" s="31" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q50" s="30" t="s">
         <v>75</v>
@@ -28120,10 +28117,10 @@
         <v>49</v>
       </c>
       <c r="Z50" s="31" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AA50" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB50" s="2" t="n">
         <f aca="false">IF(Z50&lt;&gt;CONCATENATE("Mtx",Y50),1,0)</f>
@@ -28136,10 +28133,10 @@
         <v>50</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G51" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H51" s="2" t="n">
         <f aca="false">IF(F51&lt;&gt;CONCATENATE("Aux",E51),1,0)</f>
@@ -28149,7 +28146,7 @@
         <v>50</v>
       </c>
       <c r="P51" s="31" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q51" s="30" t="s">
         <v>75</v>
@@ -28163,10 +28160,10 @@
         <v>50</v>
       </c>
       <c r="Z51" s="31" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AA51" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB51" s="2" t="n">
         <f aca="false">IF(Z51&lt;&gt;CONCATENATE("Mtx",Y51),1,0)</f>
@@ -28179,10 +28176,10 @@
         <v>51</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G52" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H52" s="2" t="n">
         <f aca="false">IF(F52&lt;&gt;CONCATENATE("Aux",E52),1,0)</f>
@@ -28192,7 +28189,7 @@
         <v>51</v>
       </c>
       <c r="P52" s="31" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q52" s="30" t="s">
         <v>75</v>
@@ -28206,10 +28203,10 @@
         <v>51</v>
       </c>
       <c r="Z52" s="31" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AA52" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB52" s="2" t="n">
         <f aca="false">IF(Z52&lt;&gt;CONCATENATE("Mtx",Y52),1,0)</f>
@@ -28222,10 +28219,10 @@
         <v>52</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G53" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H53" s="2" t="n">
         <f aca="false">IF(F53&lt;&gt;CONCATENATE("Aux",E53),1,0)</f>
@@ -28235,7 +28232,7 @@
         <v>52</v>
       </c>
       <c r="P53" s="31" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q53" s="30" t="s">
         <v>75</v>
@@ -28249,10 +28246,10 @@
         <v>52</v>
       </c>
       <c r="Z53" s="31" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AA53" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB53" s="2" t="n">
         <f aca="false">IF(Z53&lt;&gt;CONCATENATE("Mtx",Y53),1,0)</f>
@@ -28265,10 +28262,10 @@
         <v>53</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G54" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H54" s="2" t="n">
         <f aca="false">IF(F54&lt;&gt;CONCATENATE("Aux",E54),1,0)</f>
@@ -28278,7 +28275,7 @@
         <v>53</v>
       </c>
       <c r="P54" s="31" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q54" s="30" t="s">
         <v>75</v>
@@ -28292,10 +28289,10 @@
         <v>53</v>
       </c>
       <c r="Z54" s="31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AA54" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB54" s="2" t="n">
         <f aca="false">IF(Z54&lt;&gt;CONCATENATE("Mtx",Y54),1,0)</f>
@@ -28308,10 +28305,10 @@
         <v>54</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G55" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H55" s="2" t="n">
         <f aca="false">IF(F55&lt;&gt;CONCATENATE("Aux",E55),1,0)</f>
@@ -28321,7 +28318,7 @@
         <v>54</v>
       </c>
       <c r="P55" s="31" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q55" s="30" t="s">
         <v>75</v>
@@ -28335,10 +28332,10 @@
         <v>54</v>
       </c>
       <c r="Z55" s="31" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AA55" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB55" s="2" t="n">
         <f aca="false">IF(Z55&lt;&gt;CONCATENATE("Mtx",Y55),1,0)</f>
@@ -28351,10 +28348,10 @@
         <v>55</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G56" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H56" s="2" t="n">
         <f aca="false">IF(F56&lt;&gt;CONCATENATE("Aux",E56),1,0)</f>
@@ -28364,7 +28361,7 @@
         <v>55</v>
       </c>
       <c r="P56" s="31" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q56" s="30" t="s">
         <v>75</v>
@@ -28378,10 +28375,10 @@
         <v>55</v>
       </c>
       <c r="Z56" s="31" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AA56" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB56" s="2" t="n">
         <f aca="false">IF(Z56&lt;&gt;CONCATENATE("Mtx",Y56),1,0)</f>
@@ -28394,10 +28391,10 @@
         <v>56</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G57" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H57" s="2" t="n">
         <f aca="false">IF(F57&lt;&gt;CONCATENATE("Aux",E57),1,0)</f>
@@ -28407,7 +28404,7 @@
         <v>56</v>
       </c>
       <c r="P57" s="31" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Q57" s="30" t="s">
         <v>75</v>
@@ -28421,10 +28418,10 @@
         <v>56</v>
       </c>
       <c r="Z57" s="31" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AA57" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB57" s="2" t="n">
         <f aca="false">IF(Z57&lt;&gt;CONCATENATE("Mtx",Y57),1,0)</f>
@@ -28437,10 +28434,10 @@
         <v>57</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G58" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H58" s="2" t="n">
         <f aca="false">IF(F58&lt;&gt;CONCATENATE("Aux",E58),1,0)</f>
@@ -28450,7 +28447,7 @@
         <v>57</v>
       </c>
       <c r="P58" s="31" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q58" s="30" t="s">
         <v>75</v>
@@ -28464,10 +28461,10 @@
         <v>57</v>
       </c>
       <c r="Z58" s="31" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AA58" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB58" s="2" t="n">
         <f aca="false">IF(Z58&lt;&gt;CONCATENATE("Mtx",Y58),1,0)</f>
@@ -28480,10 +28477,10 @@
         <v>58</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G59" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H59" s="2" t="n">
         <f aca="false">IF(F59&lt;&gt;CONCATENATE("Aux",E59),1,0)</f>
@@ -28493,7 +28490,7 @@
         <v>58</v>
       </c>
       <c r="P59" s="31" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Q59" s="30" t="s">
         <v>75</v>
@@ -28507,10 +28504,10 @@
         <v>58</v>
       </c>
       <c r="Z59" s="31" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AA59" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB59" s="2" t="n">
         <f aca="false">IF(Z59&lt;&gt;CONCATENATE("Mtx",Y59),1,0)</f>
@@ -28523,10 +28520,10 @@
         <v>59</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G60" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H60" s="2" t="n">
         <f aca="false">IF(F60&lt;&gt;CONCATENATE("Aux",E60),1,0)</f>
@@ -28536,7 +28533,7 @@
         <v>59</v>
       </c>
       <c r="P60" s="31" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q60" s="30" t="s">
         <v>75</v>
@@ -28550,10 +28547,10 @@
         <v>59</v>
       </c>
       <c r="Z60" s="31" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AA60" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB60" s="2" t="n">
         <f aca="false">IF(Z60&lt;&gt;CONCATENATE("Mtx",Y60),1,0)</f>
@@ -28566,10 +28563,10 @@
         <v>60</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G61" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H61" s="2" t="n">
         <f aca="false">IF(F61&lt;&gt;CONCATENATE("Aux",E61),1,0)</f>
@@ -28579,7 +28576,7 @@
         <v>60</v>
       </c>
       <c r="P61" s="31" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q61" s="30" t="s">
         <v>75</v>
@@ -28593,10 +28590,10 @@
         <v>60</v>
       </c>
       <c r="Z61" s="31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AA61" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB61" s="2" t="n">
         <f aca="false">IF(Z61&lt;&gt;CONCATENATE("Mtx",Y61),1,0)</f>
@@ -28609,10 +28606,10 @@
         <v>61</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G62" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H62" s="2" t="n">
         <f aca="false">IF(F62&lt;&gt;CONCATENATE("Aux",E62),1,0)</f>
@@ -28622,7 +28619,7 @@
         <v>61</v>
       </c>
       <c r="P62" s="31" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="Q62" s="30" t="s">
         <v>75</v>
@@ -28636,10 +28633,10 @@
         <v>61</v>
       </c>
       <c r="Z62" s="31" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AA62" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB62" s="2" t="n">
         <f aca="false">IF(Z62&lt;&gt;CONCATENATE("Mtx",Y62),1,0)</f>
@@ -28652,10 +28649,10 @@
         <v>62</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G63" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H63" s="2" t="n">
         <f aca="false">IF(F63&lt;&gt;CONCATENATE("Aux",E63),1,0)</f>
@@ -28665,7 +28662,7 @@
         <v>62</v>
       </c>
       <c r="P63" s="31" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q63" s="30" t="s">
         <v>75</v>
@@ -28679,10 +28676,10 @@
         <v>62</v>
       </c>
       <c r="Z63" s="31" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AA63" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AB63" s="2" t="n">
         <f aca="false">IF(Z63&lt;&gt;CONCATENATE("Mtx",Y63),1,0)</f>
@@ -28793,15 +28790,15 @@
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="34"/>
       <c r="B1" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>529</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B2" s="28" t="n">
         <f aca="false">Groups!R65</f>
@@ -28814,7 +28811,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B3" s="28" t="n">
         <f aca="false">Groups!AL65</f>
@@ -28827,7 +28824,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B4" s="28" t="n">
         <f aca="false">Groups!H65</f>
@@ -28840,7 +28837,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">Groups!AB65</f>
@@ -28854,7 +28851,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="99.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
@@ -28891,24 +28888,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>535</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="13" t="s">
         <v>536</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B2" s="10" t="n">
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
